--- a/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -427,8 +427,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>17.4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>16.9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>18.8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>18.4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>17.8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>18.8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -722,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>16.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>18.5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>18.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -582,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>17.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -680,7 +680,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -722,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>18.4</v>
       </c>
     </row>
     <row r="26" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>18.7</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>18.1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>13.5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22">
-        <v>18.1</v>
+      <c r="D22" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25">
-        <v>18.4</v>
+      <c r="D25" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:4">
